--- a/output/pdf_financials_xlsx/BGLD.xlsx
+++ b/output/pdf_financials_xlsx/BGLD.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.54753</v>
+        <v>-0.54753</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.357775</v>
+        <v>-0.357775</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.879807</v>
+        <v>-0.879807</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.54753</v>
+        <v>-0.54753</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.357775</v>
+        <v>-0.357775</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.879807</v>
+        <v>-0.879807</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.54753</v>
+        <v>-0.54753</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.357775</v>
+        <v>-0.357775</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.879807</v>
+        <v>-0.879807</v>
       </c>
     </row>
     <row r="24">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.54753</v>
+        <v>-0.54753</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.357775</v>
+        <v>-0.357775</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.879807</v>
+        <v>-0.879807</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.54753</v>
+        <v>-0.54753</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.361657</v>
+        <v>-0.353893</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.903099</v>
+        <v>-0.856515</v>
       </c>
     </row>
     <row r="30">
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.54753</v>
+        <v>-0.54753</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.357775</v>
+        <v>-0.357775</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.879807</v>
+        <v>-0.879807</v>
       </c>
     </row>
     <row r="100">
@@ -4576,13 +4576,13 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.54753</v>
+        <v>-0.54753</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.357775</v>
+        <v>-0.357775</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.879807</v>
+        <v>-0.879807</v>
       </c>
     </row>
     <row r="62">

--- a/output/pdf_financials_xlsx/BGLD.xlsx
+++ b/output/pdf_financials_xlsx/BGLD.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.207246</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.259121</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.231232</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.207246</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.259121</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.231232</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.220569</v>
+        <v>0.013323</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.259121</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.231232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.002718</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03252</v>
       </c>
     </row>
     <row r="125">
@@ -2456,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.002718</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03252</v>
       </c>
     </row>
     <row r="126">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3750,7 +3750,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -4390,7 +4394,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">

--- a/output/pdf_financials_xlsx/BGLD.xlsx
+++ b/output/pdf_financials_xlsx/BGLD.xlsx
@@ -2072,10 +2072,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.01196</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
     </row>
     <row r="102">
@@ -2152,10 +2152,10 @@
         <v>0.060808</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.037315</v>
+        <v>0.025355</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.02709</v>
+        <v>0.027124</v>
       </c>
     </row>
     <row r="107">
@@ -3442,7 +3442,11 @@
           <t>Net income/(loss) $</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -3562,7 +3566,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -3915,7 +3923,11 @@
           <t>Net Income (Loss) $</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-0.54753</v>
       </c>
